--- a/selenium_model/PERFORMANCE_TEST_350_REPORT.xlsx
+++ b/selenium_model/PERFORMANCE_TEST_350_REPORT.xlsx
@@ -3428,7 +3428,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F216" t="n">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F258" t="n">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F300" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F301" t="n">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F311" t="n">
